--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1514"/>
+  <dimension ref="A1:B1515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15570,6 +15570,16 @@
         <v>1445</v>
       </c>
     </row>
+    <row r="1515">
+      <c r="A1515" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B1515" t="n">
+        <v>1446.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1515"/>
+  <dimension ref="A1:B1540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15580,6 +15580,256 @@
         <v>1446.1</v>
       </c>
     </row>
+    <row r="1516">
+      <c r="A1516" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B1516" t="n">
+        <v>1427.5</v>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B1517" t="n">
+        <v>1432.5</v>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B1518" t="n">
+        <v>1466.5</v>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B1519" t="n">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B1520" t="n">
+        <v>1463.5</v>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B1521" t="n">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B1522" t="n">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B1523" t="n">
+        <v>1467.5</v>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B1524" t="n">
+        <v>1475.5</v>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B1525" t="n">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B1526" t="n">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B1527" t="n">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B1528" t="n">
+        <v>1491.5</v>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B1529" t="n">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B1530" t="n">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B1531" t="n">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B1532" t="n">
+        <v>1506.5</v>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B1533" t="n">
+        <v>1489.5</v>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B1534" t="n">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B1535" t="n">
+        <v>1504.5</v>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B1536" t="n">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B1537" t="n">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B1538" t="n">
+        <v>1517.5</v>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B1539" t="n">
+        <v>1510.5</v>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B1540" t="n">
+        <v>1504.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,16 +413,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1540"/>
+  <dimension ref="A1:B1566"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
@@ -15828,6 +15816,266 @@
       </c>
       <c r="B1540" t="n">
         <v>1504.5</v>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B1541" t="n">
+        <v>1512.5</v>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B1542" t="n">
+        <v>1513.5</v>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B1543" t="n">
+        <v>1508.5</v>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B1544" t="n">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B1545" t="n">
+        <v>1481</v>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1546" t="n">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B1547" t="n">
+        <v>1489.2</v>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B1548" t="n">
+        <v>1480.5</v>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B1549" t="n">
+        <v>1473.5</v>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B1550" t="n">
+        <v>1476.5</v>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B1551" t="n">
+        <v>1480.8</v>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B1552" t="n">
+        <v>1479.3</v>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B1553" t="n">
+        <v>1472.3</v>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B1554" t="n">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B1555" t="n">
+        <v>1479.5</v>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B1556" t="n">
+        <v>1484</v>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B1557" t="n">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B1558" t="n">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B1559" t="n">
+        <v>1474.5</v>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B1560" t="n">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B1561" t="n">
+        <v>1475.5</v>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B1562" t="n">
+        <v>1469</v>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B1563" t="n">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B1564" t="n">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B1565" t="n">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="A1566" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1566" t="n">
+        <v>1475</v>
       </c>
     </row>
   </sheetData>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,16 +425,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1566"/>
+  <dimension ref="A1:B1588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
@@ -16076,6 +16088,226 @@
       </c>
       <c r="B1566" t="n">
         <v>1475</v>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1567" t="n">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="1568">
+      <c r="A1568" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1568" t="n">
+        <v>1489.5</v>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1569" t="n">
+        <v>1493.5</v>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1570" t="n">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1571" t="n">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B1572" t="n">
+        <v>1507.8</v>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B1573" t="n">
+        <v>1498.5</v>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B1574" t="n">
+        <v>1505.5</v>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B1575" t="n">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B1576" t="n">
+        <v>1507.5</v>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B1577" t="n">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B1578" t="n">
+        <v>1496.5</v>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B1579" t="n">
+        <v>1507.5</v>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B1580" t="n">
+        <v>1514.5</v>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B1581" t="n">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B1582" t="n">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B1583" t="n">
+        <v>1559.5</v>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B1584" t="n">
+        <v>1527.8</v>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B1585" t="n">
+        <v>1524.5</v>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B1586" t="n">
+        <v>1524.5</v>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B1587" t="n">
+        <v>1519</v>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B1588" t="n">
+        <v>1521</v>
       </c>
     </row>
   </sheetData>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1588"/>
+  <dimension ref="A1:B1600"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16310,6 +16310,126 @@
         <v>1521</v>
       </c>
     </row>
+    <row r="1589">
+      <c r="A1589" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B1589" t="n">
+        <v>1515.5</v>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B1590" t="n">
+        <v>1511</v>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B1591" t="n">
+        <v>1525.5</v>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B1592" t="n">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B1593" t="n">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B1594" t="n">
+        <v>1538.5</v>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B1595" t="n">
+        <v>1533.5</v>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B1596" t="n">
+        <v>1543.5</v>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B1597" t="n">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B1598" t="n">
+        <v>1537.5</v>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B1599" t="n">
+        <v>1541.5</v>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B1600" t="n">
+        <v>1542</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1600"/>
+  <dimension ref="A1:B1601"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16430,6 +16430,16 @@
         <v>1542</v>
       </c>
     </row>
+    <row r="1601">
+      <c r="A1601" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B1601" t="n">
+        <v>1552.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1601"/>
+  <dimension ref="A1:B1602"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16440,6 +16440,16 @@
         <v>1552.5</v>
       </c>
     </row>
+    <row r="1602">
+      <c r="A1602" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B1602" t="n">
+        <v>1542.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1602"/>
+  <dimension ref="A1:B1604"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16450,6 +16450,26 @@
         <v>1542.5</v>
       </c>
     </row>
+    <row r="1603">
+      <c r="A1603" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B1603" t="n">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B1604" t="n">
+        <v>1530.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1604"/>
+  <dimension ref="A1:B1605"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16470,6 +16470,16 @@
         <v>1530.5</v>
       </c>
     </row>
+    <row r="1605">
+      <c r="A1605" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B1605" t="n">
+        <v>1517.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1605"/>
+  <dimension ref="A1:B1606"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16480,6 +16480,16 @@
         <v>1517.2</v>
       </c>
     </row>
+    <row r="1606">
+      <c r="A1606" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B1606" t="n">
+        <v>1507</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1606"/>
+  <dimension ref="A1:B1607"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16490,6 +16490,16 @@
         <v>1507</v>
       </c>
     </row>
+    <row r="1607">
+      <c r="A1607" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B1607" t="n">
+        <v>1507</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1607"/>
+  <dimension ref="A1:B1609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16500,6 +16500,26 @@
         <v>1507</v>
       </c>
     </row>
+    <row r="1608">
+      <c r="A1608" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B1608" t="n">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B1609" t="n">
+        <v>1502</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1609"/>
+  <dimension ref="A1:B1613"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16520,6 +16520,46 @@
         <v>1502</v>
       </c>
     </row>
+    <row r="1610">
+      <c r="A1610" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B1610" t="n">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B1611" t="n">
+        <v>1488.5</v>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B1612" t="n">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="A1613" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1613" t="n">
+        <v>1484.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1613"/>
+  <dimension ref="A1:B1615"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16560,6 +16560,26 @@
         <v>1484.4</v>
       </c>
     </row>
+    <row r="1614">
+      <c r="A1614" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B1614" t="n">
+        <v>1482.5</v>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B1615" t="n">
+        <v>1481</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1615"/>
+  <dimension ref="A1:B1616"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16580,6 +16580,16 @@
         <v>1481</v>
       </c>
     </row>
+    <row r="1616">
+      <c r="A1616" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B1616" t="n">
+        <v>1476.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1616"/>
+  <dimension ref="A1:B1617"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16590,6 +16590,16 @@
         <v>1476.5</v>
       </c>
     </row>
+    <row r="1617">
+      <c r="A1617" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B1617" t="n">
+        <v>1462.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1617"/>
+  <dimension ref="A1:B1618"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16600,6 +16600,16 @@
         <v>1462.5</v>
       </c>
     </row>
+    <row r="1618">
+      <c r="A1618" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B1618" t="n">
+        <v>1466</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1618"/>
+  <dimension ref="A1:B1619"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16610,6 +16610,16 @@
         <v>1466</v>
       </c>
     </row>
+    <row r="1619">
+      <c r="A1619" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B1619" t="n">
+        <v>1455.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1619"/>
+  <dimension ref="A1:B1620"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16620,6 +16620,16 @@
         <v>1455.2</v>
       </c>
     </row>
+    <row r="1620">
+      <c r="A1620" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B1620" t="n">
+        <v>1446</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1620"/>
+  <dimension ref="A1:B1621"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16630,6 +16630,16 @@
         <v>1446</v>
       </c>
     </row>
+    <row r="1621">
+      <c r="A1621" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B1621" t="n">
+        <v>1426.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1621"/>
+  <dimension ref="A1:B1622"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16640,6 +16640,16 @@
         <v>1426.2</v>
       </c>
     </row>
+    <row r="1622">
+      <c r="A1622" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B1622" t="n">
+        <v>1440</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1622"/>
+  <dimension ref="A1:B1624"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16650,6 +16650,26 @@
         <v>1440</v>
       </c>
     </row>
+    <row r="1623">
+      <c r="A1623" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B1623" t="n">
+        <v>1430.8</v>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B1624" t="n">
+        <v>1424.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1624"/>
+  <dimension ref="A1:B1625"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16670,6 +16670,16 @@
         <v>1424.4</v>
       </c>
     </row>
+    <row r="1625">
+      <c r="A1625" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B1625" t="n">
+        <v>1423.6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1625"/>
+  <dimension ref="A1:B1626"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16680,6 +16680,16 @@
         <v>1423.6</v>
       </c>
     </row>
+    <row r="1626">
+      <c r="A1626" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B1626" t="n">
+        <v>1424.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1626"/>
+  <dimension ref="A1:B1627"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16690,6 +16690,16 @@
         <v>1424.5</v>
       </c>
     </row>
+    <row r="1627">
+      <c r="A1627" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B1627" t="n">
+        <v>1411</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1627"/>
+  <dimension ref="A1:B1628"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16700,6 +16700,16 @@
         <v>1411</v>
       </c>
     </row>
+    <row r="1628">
+      <c r="A1628" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1628" t="n">
+        <v>1419.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1628"/>
+  <dimension ref="A1:B1629"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16710,6 +16710,16 @@
         <v>1419.5</v>
       </c>
     </row>
+    <row r="1629">
+      <c r="A1629" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B1629" t="n">
+        <v>1413.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1629"/>
+  <dimension ref="A1:B1630"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16720,6 +16720,16 @@
         <v>1413.4</v>
       </c>
     </row>
+    <row r="1630">
+      <c r="A1630" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B1630" t="n">
+        <v>1419</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1630"/>
+  <dimension ref="A1:B1631"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16730,6 +16730,16 @@
         <v>1419</v>
       </c>
     </row>
+    <row r="1631">
+      <c r="A1631" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1631" t="n">
+        <v>1420.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1631"/>
+  <dimension ref="A1:B1632"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16740,6 +16740,16 @@
         <v>1420.2</v>
       </c>
     </row>
+    <row r="1632">
+      <c r="A1632" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1632" t="n">
+        <v>1417.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1632"/>
+  <dimension ref="A1:B1633"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16750,6 +16750,16 @@
         <v>1417.5</v>
       </c>
     </row>
+    <row r="1633">
+      <c r="A1633" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1633" t="n">
+        <v>1413.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1633"/>
+  <dimension ref="A1:B1634"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16760,6 +16760,16 @@
         <v>1413.5</v>
       </c>
     </row>
+    <row r="1634">
+      <c r="A1634" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1634" t="n">
+        <v>1390</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1634"/>
+  <dimension ref="A1:B1635"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16770,6 +16770,16 @@
         <v>1390</v>
       </c>
     </row>
+    <row r="1635">
+      <c r="A1635" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1635" t="n">
+        <v>1394.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1635"/>
+  <dimension ref="A1:B1636"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16780,6 +16780,16 @@
         <v>1394.3</v>
       </c>
     </row>
+    <row r="1636">
+      <c r="A1636" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1636" t="n">
+        <v>1387</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1636"/>
+  <dimension ref="A1:B1637"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16790,6 +16790,16 @@
         <v>1387</v>
       </c>
     </row>
+    <row r="1637">
+      <c r="A1637" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1637" t="n">
+        <v>1385.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1637"/>
+  <dimension ref="A1:B1638"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16800,6 +16800,16 @@
         <v>1385.5</v>
       </c>
     </row>
+    <row r="1638">
+      <c r="A1638" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B1638" t="n">
+        <v>1383</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1638"/>
+  <dimension ref="A1:B1639"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16810,6 +16810,16 @@
         <v>1383</v>
       </c>
     </row>
+    <row r="1639">
+      <c r="A1639" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1639" t="n">
+        <v>1384.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1639"/>
+  <dimension ref="A1:B1640"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16820,6 +16820,16 @@
         <v>1384.8</v>
       </c>
     </row>
+    <row r="1640">
+      <c r="A1640" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1640" t="n">
+        <v>1382</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1640"/>
+  <dimension ref="A1:B1642"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16830,6 +16830,26 @@
         <v>1382</v>
       </c>
     </row>
+    <row r="1641">
+      <c r="A1641" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1641" t="n">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1642" t="n">
+        <v>1380</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1642"/>
+  <dimension ref="A1:B1643"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16850,6 +16850,16 @@
         <v>1380</v>
       </c>
     </row>
+    <row r="1643">
+      <c r="A1643" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1643" t="n">
+        <v>1375.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1643"/>
+  <dimension ref="A1:B1644"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16860,6 +16860,16 @@
         <v>1375.5</v>
       </c>
     </row>
+    <row r="1644">
+      <c r="A1644" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1644" t="n">
+        <v>1360.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1644"/>
+  <dimension ref="A1:B1647"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16870,6 +16870,36 @@
         <v>1360.3</v>
       </c>
     </row>
+    <row r="1645">
+      <c r="A1645" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B1645" t="n">
+        <v>1358.5</v>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B1646" t="n">
+        <v>1349.5</v>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1647" t="n">
+        <v>1347</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/0_raw/exchange_rate_data.xlsx
+++ b/data/0_raw/exchange_rate_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1647"/>
+  <dimension ref="A1:B1650"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16900,6 +16900,36 @@
         <v>1347</v>
       </c>
     </row>
+    <row r="1648">
+      <c r="A1648" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B1648" t="n">
+        <v>1341.5</v>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B1649" t="n">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B1650" t="n">
+        <v>1338.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
